--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\Ticket‘ｓフォルダー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\DailyScrum\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -334,6 +334,47 @@
     <t>議事録</t>
     <rPh sb="0" eb="3">
       <t>ギジロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/17
+(木)</t>
+    <rPh sb="11" eb="12">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱上のスコア表示＿</t>
+    <rPh sb="3" eb="5">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴールした時のUI表示_
+・ゲームのクリア処理_
+・NPCに近づくと吹き飛ばされる処理_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・データをランダムで3つ重複なしで選択表示_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・周りの背景の変更作業＿</t>
+    <rPh sb="1" eb="2">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ヘンコウサギョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -397,7 +438,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -407,11 +448,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -703,12 +750,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -725,7 +772,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -739,7 +786,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -751,7 +798,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -763,7 +810,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -774,10 +821,51 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:A11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -338,35 +338,162 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2026/4/17
-(木)</t>
-    <rPh sb="11" eb="12">
-      <t>モク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゴミ箱上のスコア表示＿</t>
+    <r>
+      <t>・ゴミ箱上のスコア表示＿完了
+・ゴミ箱(ゴール)のプログラムとゴミ箱の上のスコア表示結合＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
     <rPh sb="3" eb="5">
       <t>バコジョウ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゴールした時のUI表示_
-・ゲームのクリア処理_
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱(ゴール)のプログラムとゴミ箱上のスコア表示の結合</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バコジョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケツゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/17(金)</t>
+    <rPh sb="10" eb="11">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームループの完成</t>
+    <rPh sb="8" eb="10">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スタート画面制作</t>
+    <rPh sb="5" eb="9">
+      <t>ガメンセイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・データをランダムで3つ重複なしで選択表示_完了
+・データの整理＿完了</t>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を実際のプロジェクトに実装</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゴールした時のUI表示_
+・ゲームのクリア処理_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 ・NPCに近づくと吹き飛ばされる処理_</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・データをランダムで3つ重複なしで選択表示_</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・周りの背景の変更作業＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>中断</t>
+    </r>
+    <rPh sb="25" eb="27">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>チュウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・周りの背景の変更作業＿完了
+・スタート画面制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
     <rPh sb="1" eb="2">
       <t>マワ</t>
     </rPh>
@@ -375,6 +502,22 @@
     </rPh>
     <rPh sb="7" eb="11">
       <t>ヘンコウサギョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ガメンセイサク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/20(月)</t>
+    <rPh sb="10" eb="11">
+      <t>ゲツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -438,12 +581,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -740,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -750,12 +896,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -772,7 +918,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -786,7 +932,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -798,7 +944,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -810,7 +956,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -821,11 +967,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -833,39 +982,73 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" s="4"/>
+    <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="5"/>
       <c r="B10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" s="4"/>
+    <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="5"/>
       <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="5"/>
+      <c r="D13" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="5"/>
+      <c r="D14" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" s="5"/>
+      <c r="D15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -519,6 +519,153 @@
     <rPh sb="10" eb="11">
       <t>ゲツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱(ゴール)のプログラムとゴミ箱上のスコア表示の結合＿完了
+・自販機で買える能力表２＿完了</t>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をオブジェクトに付与</t>
+    <rPh sb="1" eb="4">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スタート画面制作＿完了
+・周りの背景の変更作業(訂正)＿完了</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ヘンコウサギョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・自販機を実際のプロジェクトに実装＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音検索＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="27">
+      <t>コウカオンケンサク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱を実際のプロジェクトに実装</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶の最終調整</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームループ＿完了
+※TIKETS-の作成</t>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を実際のプロジェクトに実装＿途中
+・効果音検索＿途中</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -526,7 +673,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,6 +705,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -581,7 +735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -605,6 +759,9 @@
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -890,8 +1047,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="46.625" customWidth="1"/>
-    <col min="3" max="3" width="33.125" customWidth="1"/>
+    <col min="2" max="2" width="58.125" customWidth="1"/>
+    <col min="3" max="3" width="39.125" customWidth="1"/>
     <col min="4" max="4" width="14.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1017,28 +1174,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A13" s="5"/>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="D13" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A14" s="5"/>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="D14" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A15" s="5"/>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="D15" s="4" t="s">
         <v>8</v>
       </c>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -569,6 +569,43 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>・ゴミ箱を実際のプロジェクトに実装</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶の最終調整</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームループ＿完了
+※TIKETS-の作成</t>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <r>
       <t>・自販機を実際のプロジェクトに実装＿</t>
     </r>
@@ -593,18 +630,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-・効果音検索＿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>途中</t>
+・効果音検索＿完了</t>
     </r>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
@@ -622,50 +648,30 @@
       <t>コウカオンケンサク</t>
     </rPh>
     <rPh sb="28" eb="30">
-      <t>トチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゴミ箱を実際のプロジェクトに実装</t>
-    <rPh sb="3" eb="4">
-      <t>バコ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジッサイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・缶の最終調整</t>
-    <rPh sb="1" eb="2">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サイシュウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・ゲームループ＿完了
-※TIKETS-の作成</t>
-    <rPh sb="8" eb="10">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・自販機を実際のプロジェクトに実装＿途中
-・効果音検索＿途中</t>
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を実際のプロジェクトに実装</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/21(火)</t>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/22(水)</t>
+    <rPh sb="10" eb="11">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -751,6 +757,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -759,9 +768,6 @@
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1043,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -1053,12 +1059,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -1075,7 +1081,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1089,7 +1095,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="5"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1101,7 +1107,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="5"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1119,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="5"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1130,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1139,7 +1145,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="5"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1151,7 +1157,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="5"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1163,7 +1169,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="5"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -1175,7 +1181,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1189,21 +1195,21 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="5"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="5"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>35</v>
@@ -1213,23 +1219,56 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="5"/>
+      <c r="A15" s="6"/>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>32</v>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" s="6"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" s="6"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" s="6"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -569,19 +569,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゴミ箱を実際のプロジェクトに実装</t>
-    <rPh sb="3" eb="4">
-      <t>バコ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジッサイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・缶の最終調整</t>
     <rPh sb="1" eb="2">
       <t>カン</t>
@@ -653,10 +640,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・自販機を実際のプロジェクトに実装</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2026/4/21(火)</t>
     <rPh sb="10" eb="11">
       <t>カ</t>
@@ -671,7 +654,195 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・</t>
+    <t>・ゴミ箱の設置</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける3(自販機)</t>
+    <rPh sb="1" eb="4">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ジハンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機のプログラム調整</t>
+    <rPh sb="10" eb="12">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のプログラム5＿完了
+・ポーズの作成＿完了</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・時間制限の作成
+・ゴミ箱のスコア見直し
+・トータルスコアの計算</t>
+    <rPh sb="1" eb="5">
+      <t>ジカンセイゲン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・カメラ調整の改良
+・自販機の設置(案)</t>
+    <rPh sb="11" eb="14">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・データの再構築＿完了
+・自販機の運ゲー要素の追加＿完了</t>
+    <rPh sb="5" eb="8">
+      <t>サイコウチク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゴミ箱の設置＿完了
+・カメラ調整の改良＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイリョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゴミ箱(ゴール)とゴミ箱上のスコア表示(訂正vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音をつける1(缶vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="43" eb="44">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱(ゴール)とゴミ箱上のスコア表示(訂正vol.1)
+・効果音をつける1(缶vol.1)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -761,13 +932,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1054,17 +1225,17 @@
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="58.125" customWidth="1"/>
-    <col min="3" max="3" width="39.125" customWidth="1"/>
+    <col min="3" max="3" width="45.5" customWidth="1"/>
     <col min="4" max="4" width="14.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -1081,7 +1252,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1095,7 +1266,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1107,7 +1278,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="6"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1119,7 +1290,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1131,7 +1302,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1145,7 +1316,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="6"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1157,7 +1328,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="6"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1169,7 +1340,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="6"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -1181,7 +1352,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1195,71 +1366,104 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="6"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>36</v>
+    <row r="16" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" s="6"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="7"/>
+      <c r="B18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6"/>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A19" s="7"/>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -845,12 +845,197 @@
 ・効果音をつける1(缶vol.1)</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <r>
+      <t>・ゴミ箱(ゴール)とゴミ箱上のスコア表示(訂正vol.1)＿完了
+・効果音をつける1(缶vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・トータルスコアの計算</t>
+    <rPh sb="9" eb="11">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機の設置
+・自販機関係UIの手直し
+・人のアルゴリズム</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テナオ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・カメラ調整の改良＿完了
+・自販機の設置(案)＿完了
+・光の柱の作成(訂正)＿完了</t>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ハシラ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・効果音をつける3(自販機)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>完了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>・自販機の購入時プログラム＿完了</t>
+    </r>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・制限時間の作成＿完了
+・UIの表示(ゲーム画面)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・UIの表示(ゲーム画面)
+・車のアルゴリズム制作</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -886,6 +1071,14 @@
       <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1401,7 +1594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
@@ -1451,19 +1644,55 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A22" s="7"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A23" s="7"/>
+      <c r="B23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -881,30 +881,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・自販機の設置
-・自販機関係UIの手直し
-・人のアルゴリズム</t>
-    <rPh sb="1" eb="4">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セッチ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カンケイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>テナオ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヒト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・カメラ調整の改良＿完了
 ・自販機の設置(案)＿完了
 ・光の柱の作成(訂正)＿完了</t>
@@ -1014,20 +990,136 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・UIの表示(ゲーム画面)
+    <t>2026/4/24(金)</t>
+    <rPh sb="10" eb="11">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/23(木)</t>
+    <rPh sb="10" eb="11">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)</t>
+  </si>
+  <si>
+    <t>・カメラなど細かい手直し
 ・車のアルゴリズム制作</t>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="15" eb="16">
+    <rPh sb="6" eb="7">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・車のアルゴリズム制作</t>
+    <rPh sb="1" eb="2">
       <t>クルマ</t>
     </rPh>
-    <rPh sb="23" eb="25">
+    <rPh sb="9" eb="11">
       <t>セイサク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・効果音をつける1(缶vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="18" eb="20">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・車のアルゴリズム制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="12" eb="14">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機の設置
+・自販機関係UIの手直し</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機の設置＿完了
+・自販機関係UIの手直し＿完了</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・人のアルゴリズム作成</t>
+    <rPh sb="1" eb="2">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・トータルスコアの計算</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける4(コイン)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1413,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -1661,22 +1753,22 @@
     <row r="21" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A21" s="7"/>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A22" s="7"/>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1685,7 +1777,7 @@
     <row r="23" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>48</v>
@@ -1694,8 +1786,74 @@
         <v>8</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A25" s="7"/>
+      <c r="B25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A26" s="7"/>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" s="7"/>
+      <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A31" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A1:D1"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -1004,9 +1004,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音をつける1(缶vol.1)</t>
-  </si>
-  <si>
     <t>・カメラなど細かい手直し
 ・車のアルゴリズム制作</t>
     <rPh sb="6" eb="7">
@@ -1088,7 +1085,69 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・自販機の設置＿完了
+    <t>・トータルスコアの計算</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける4(コイン)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・効果音をつける1(缶vol.1)→譲渡
+・ゴミ箱のプロジェクト移動＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="18" eb="20">
+      <t>ジョウト</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/27(月)</t>
+    <rPh sb="10" eb="11">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/4/28(火)</t>
+    <rPh sb="10" eb="11">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・カメラなど細かい手直し＿完了
+</t>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機の設置(再)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機の設置＿途中
 ・自販機関係UIの手直し＿完了</t>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
@@ -1097,7 +1156,7 @@
       <t>セッチ</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>カンリョウ</t>
+      <t>トチュウ</t>
     </rPh>
     <rPh sb="24" eb="26">
       <t>カンリョウ</t>
@@ -1105,21 +1164,415 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・人のアルゴリズム作成</t>
+    <t>・自販機の設置
+・人のアルゴリズム作成</t>
+    <rPh sb="9" eb="10">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱のプロジェクト移動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームオーバー処理
+・ドリンクなどの効果見直し</t>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱のクリア処理
+・ゴミ箱のスコア見直し→後</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・自販機の設置(再)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・自販機のスクリプト＿完了</t>
+    </r>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・コインの上下をなくす＿完了
+・シャカゲージの作成＿完了
+・ゴミ箱のスコア見直し＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="5" eb="7">
+      <t>ジョウゲ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Final版に向けて</t>
+    <rPh sb="5" eb="6">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の表示スコア直し＿完了
+・ドリンクのタイマー＿完了</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゴミ箱のプロジェクト移行＿完了
+・効果音をつける4(コイン)＿完了
+・ゲームBGMの再生＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゲームループ＿完了(多分)
+・車のアルゴリズム作成＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タブン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・自販機の設置＿完了
+・自販機のスクリプトの修正＿完了
+・缶のステータス＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームBGMの再生
+・ゲーム説明制作
+・車の配置(案)
+・効果音の切り取り</t>
+    <rPh sb="8" eb="10">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>セツメイセイサク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・車のアルゴリズム作成
+・場外の判定や轢かれた時のリザルト
+・効果音をつける1(缶vol.1)
+・効果音をつける2(缶vol.2)
+・効果音をつける6(車)</t>
     <rPh sb="1" eb="2">
-      <t>ヒト</t>
+      <t>クルマ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・トータルスコアの計算</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・効果音をつける4(コイン)</t>
+    <rPh sb="13" eb="14">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ソト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="67" eb="70">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>クルマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のステータス
+・能力自販機と缶の紐付
+・効果音をつける5(人)
+・NPCが缶を蹴るプログラム</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>ノウリョクジハンキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒモ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヅケ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPCの配置(案)
+・すべてのゴミ箱を光らせる関数
+・コインの取得範囲の上昇の関数</t>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンスウ</t>
+    </rPh>
+    <rPh sb="32" eb="36">
+      <t>シュトクハンイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンスウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1127,7 +1580,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1174,13 +1627,26 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1192,12 +1658,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1225,8 +1694,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="悪い" xfId="1" builtinId="27"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1505,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -1756,7 +2235,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>6</v>
@@ -1768,7 +2247,7 @@
         <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1791,10 +2270,10 @@
         <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -1803,10 +2282,10 @@
     <row r="25" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A25" s="7"/>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>6</v>
@@ -1815,10 +2294,10 @@
     <row r="26" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A26" s="7"/>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -1827,39 +2306,150 @@
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="7"/>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A29" s="7"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A31" s="7"/>
+      <c r="B31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="11"/>
+    </row>
+    <row r="33" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="7"/>
+      <c r="B34" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A35" s="7"/>
+      <c r="B35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A36" s="7"/>
+      <c r="B36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A37" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A38" s="7"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A40" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A20:A23"/>
+  <mergeCells count="11">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A32:C32"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -1572,6 +1572,177 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のステータス＿途中
+・能力自販機と缶の紐付＿途中
+・効果音をつける5(人)＿完了
+・NPCが缶を蹴るプログラム＿完了</t>
+    <rPh sb="9" eb="11">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPCの配置(案)＿完了
+・すべてのゴミ箱を光らせる関数＿未
+・コインの取得範囲の上昇の関数＿未</t>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作
+・車の配置(案)
+・効果音の切り取り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)
+・効果音をつける2(缶vol.2)
+・効果音をつける6(車)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・車のアルゴリズム作成＿完了
+・場外の判定や轢かれた時のリザルト＿完了
+・効果音をつける1(缶vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音をつける2(缶vol.2)＿未
+・効果音をつける6(車)＿未</t>
+    </r>
+    <rPh sb="12" eb="14">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゲームBGMの再生＿完了
+・ゲーム説明制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・車の配置(案)＿未
+・効果音の切り取り＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のステータス
+・能力自販機と缶の紐付</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・すべてのゴミ箱を光らせる関数
+・コインの取得範囲の上昇の関数</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/5/7(木)</t>
+    <rPh sb="9" eb="10">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026/5/8(金)</t>
+    <rPh sb="9" eb="10">
+      <t>キン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1685,8 +1856,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1694,13 +1868,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="56" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1984,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.375" style="2" customWidth="1"/>
@@ -1994,12 +2165,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -2016,7 +2187,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2030,7 +2201,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2042,7 +2213,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -2054,7 +2225,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2066,7 +2237,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2080,7 +2251,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="7"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2092,7 +2263,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="7"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
@@ -2104,7 +2275,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -2116,7 +2287,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2130,7 +2301,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="7"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2142,7 +2313,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="7"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
@@ -2154,7 +2325,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="7"/>
+      <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
@@ -2166,7 +2337,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2180,7 +2351,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A17" s="7"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
@@ -2192,7 +2363,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="7"/>
+      <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
@@ -2204,7 +2375,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
@@ -2216,7 +2387,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2230,7 +2401,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
@@ -2242,7 +2413,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A22" s="7"/>
+      <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
@@ -2254,7 +2425,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="7"/>
+      <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,7 +2437,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B24" t="s">
@@ -2280,7 +2451,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="7"/>
+      <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
@@ -2292,7 +2463,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A26" s="7"/>
+      <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>67</v>
       </c>
@@ -2304,7 +2475,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" s="7"/>
+      <c r="A27" s="8"/>
       <c r="B27" s="1" t="s">
         <v>59</v>
       </c>
@@ -2316,7 +2487,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2330,7 +2501,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A29" s="7"/>
+      <c r="A29" s="8"/>
       <c r="B29" s="1" t="s">
         <v>65</v>
       </c>
@@ -2342,7 +2513,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A30" s="7"/>
+      <c r="A30" s="8"/>
       <c r="B30" s="1" t="s">
         <v>72</v>
       </c>
@@ -2354,7 +2525,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A31" s="7"/>
+      <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>73</v>
       </c>
@@ -2366,18 +2537,18 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2388,8 +2559,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="7"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2400,8 +2571,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A35" s="7"/>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2412,7 +2583,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A36" s="7"/>
+      <c r="A36" s="8"/>
       <c r="B36" s="1" t="s">
         <v>75</v>
       </c>
@@ -2423,33 +2594,99 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A37" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A40" s="7"/>
+      <c r="B37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A38" s="8"/>
+      <c r="B38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.4">
+      <c r="A39" s="8"/>
+      <c r="B39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A40" s="8"/>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A41" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A42" s="8"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A45" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A46" s="8"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A48" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
+  <mergeCells count="13">
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
     <mergeCell ref="A33:A36"/>
     <mergeCell ref="A37:A40"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -1595,21 +1595,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・NPCの配置(案)＿完了
-・すべてのゴミ箱を光らせる関数＿未
-・コインの取得範囲の上昇の関数＿未</t>
-    <rPh sb="11" eb="13">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・ゲーム説明制作
 ・車の配置(案)
 ・効果音の切り取り</t>
@@ -1728,11 +1713,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・すべてのゴミ箱を光らせる関数
-・コインの取得範囲の上昇の関数</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2026/5/7(木)</t>
     <rPh sb="9" eb="10">
       <t>モク</t>
@@ -1743,6 +1723,31 @@
     <t>2026/5/8(金)</t>
     <rPh sb="9" eb="10">
       <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPCの配置(案)＿完了
+・すべてのゴミ箱を光らせる関数＿完了
+・コインの取得範囲の上昇の関数＿完了</t>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・制限時間の調整</t>
+    <rPh sb="1" eb="5">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1863,15 +1868,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2165,12 +2170,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -2187,7 +2192,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2201,7 +2206,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="8"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2213,7 +2218,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -2225,7 +2230,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2237,7 +2242,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2251,7 +2256,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
+      <c r="A9" s="9"/>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2263,7 +2268,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="8"/>
+      <c r="A10" s="9"/>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
@@ -2275,7 +2280,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="8"/>
+      <c r="A11" s="9"/>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
@@ -2287,7 +2292,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2301,7 +2306,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="8"/>
+      <c r="A13" s="9"/>
       <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2313,7 +2318,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="8"/>
+      <c r="A14" s="9"/>
       <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
@@ -2325,7 +2330,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="8"/>
+      <c r="A15" s="9"/>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
@@ -2337,7 +2342,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2351,7 +2356,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A17" s="8"/>
+      <c r="A17" s="9"/>
       <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
@@ -2363,7 +2368,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="8"/>
+      <c r="A18" s="9"/>
       <c r="B18" s="1" t="s">
         <v>42</v>
       </c>
@@ -2375,7 +2380,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="8"/>
+      <c r="A19" s="9"/>
       <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
@@ -2387,7 +2392,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2401,7 +2406,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A21" s="8"/>
+      <c r="A21" s="9"/>
       <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
@@ -2413,7 +2418,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A22" s="8"/>
+      <c r="A22" s="9"/>
       <c r="B22" s="1" t="s">
         <v>50</v>
       </c>
@@ -2425,7 +2430,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A23" s="8"/>
+      <c r="A23" s="9"/>
       <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
@@ -2437,7 +2442,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B24" t="s">
@@ -2451,7 +2456,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="8"/>
+      <c r="A25" s="9"/>
       <c r="B25" s="1" t="s">
         <v>57</v>
       </c>
@@ -2463,7 +2468,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A26" s="8"/>
+      <c r="A26" s="9"/>
       <c r="B26" s="1" t="s">
         <v>67</v>
       </c>
@@ -2475,7 +2480,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A27" s="8"/>
+      <c r="A27" s="9"/>
       <c r="B27" s="1" t="s">
         <v>59</v>
       </c>
@@ -2487,7 +2492,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2501,7 +2506,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A29" s="8"/>
+      <c r="A29" s="9"/>
       <c r="B29" s="1" t="s">
         <v>65</v>
       </c>
@@ -2513,7 +2518,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A30" s="8"/>
+      <c r="A30" s="9"/>
       <c r="B30" s="1" t="s">
         <v>72</v>
       </c>
@@ -2525,7 +2530,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A31" s="8"/>
+      <c r="A31" s="9"/>
       <c r="B31" s="1" t="s">
         <v>73</v>
       </c>
@@ -2537,15 +2542,15 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -2559,7 +2564,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="8"/>
+      <c r="A34" s="9"/>
       <c r="B34" s="6" t="s">
         <v>77</v>
       </c>
@@ -2571,7 +2576,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A35" s="8"/>
+      <c r="A35" s="9"/>
       <c r="B35" s="6" t="s">
         <v>78</v>
       </c>
@@ -2583,7 +2588,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A36" s="8"/>
+      <c r="A36" s="9"/>
       <c r="B36" s="1" t="s">
         <v>75</v>
       </c>
@@ -2595,91 +2600,85 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A38" s="8"/>
+      <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.4">
-      <c r="A39" s="8"/>
+      <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A40" s="8"/>
+      <c r="A40" s="9"/>
       <c r="B40" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A41" s="10" t="s">
-        <v>91</v>
+      <c r="A41" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A42" s="8"/>
+      <c r="A42" s="9"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A43" s="8"/>
+      <c r="A43" s="9"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A44" s="8"/>
+      <c r="A44" s="9"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A45" s="10" t="s">
-        <v>92</v>
+      <c r="A45" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A46" s="8"/>
+      <c r="A46" s="9"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A47" s="8"/>
+      <c r="A47" s="9"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A48" s="8"/>
+      <c r="A48" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A4:A7"/>
@@ -2687,6 +2686,12 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -1576,37 +1576,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・缶のステータス＿途中
-・能力自販機と缶の紐付＿途中
-・効果音をつける5(人)＿完了
-・NPCが缶を蹴るプログラム＿完了</t>
-    <rPh sb="9" eb="11">
-      <t>トチュウ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>トチュウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・ゲーム説明制作
 ・車の配置(案)
 ・効果音の切り取り</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音をつける1(缶vol.1)
-・効果音をつける2(缶vol.2)
-・効果音をつける6(車)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <t>・車のアルゴリズム作成＿完了
 ・場外の判定や轢かれた時のリザルト＿完了
@@ -1705,11 +1680,6 @@
     <rPh sb="47" eb="49">
       <t>トチュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・缶のステータス
-・能力自販機と缶の紐付</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1748,6 +1718,216 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のステータス
+・能力自販機と缶の紐付</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶のステータス＿完了
+・能力自販機と缶の紐付＿完了</t>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作
+・効果音の切り取り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)
+・効果音をつける2(缶vol.2)
+・効果音をつける6(車)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)
+・効果音をつける2(缶vol.2)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームのバグ探し</t>
+    <rPh sb="7" eb="8">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・制限時間の調整＿完了</t>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・車の配置
+・プレゼンテーション作成</t>
+    <rPh sb="1" eb="2">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・缶のステータス＿途中
+・能力自販機と缶の紐付＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音をつける5(人)＿完了
+・NPCが缶を蹴るプログラム＿完了</t>
+    </r>
+    <rPh sb="9" eb="11">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・ゲーム説明制作＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音の切り取り＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <rPh sb="9" eb="11">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・効果音をつける1(缶vol.1)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音をつける2(缶vol.2)＿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>途中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+・効果音をつける6(車)＿完了</t>
+    </r>
+    <rPh sb="18" eb="20">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2604,10 +2784,10 @@
         <v>64</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -2616,10 +2796,10 @@
     <row r="38" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A38" s="9"/>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>6</v>
@@ -2628,10 +2808,10 @@
     <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.4">
       <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>7</v>
@@ -2640,32 +2820,68 @@
     <row r="40" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A40" s="9"/>
       <c r="B40" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A41" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
+      <c r="B44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -2679,6 +2895,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A4:A7"/>
@@ -2686,12 +2908,6 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Reports/DailyScrum/議事録.xlsx
+++ b/Reports/DailyScrum/議事録.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="109">
   <si>
     <t>昨日の作業</t>
     <rPh sb="0" eb="2">
@@ -1738,11 +1738,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ゲーム説明制作
-・効果音の切り取り</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・効果音をつける1(缶vol.1)
 ・効果音をつける2(缶vol.2)
 ・効果音をつける6(車)</t>
@@ -1928,6 +1923,170 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作
+・効果音の切り取り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲーム説明制作＿完了
+・効果音の切り取り＿完了</t>
+    <rPh sb="9" eb="11">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音をつける1(缶vol.1)＿完了
+・効果音をつける2(缶vol.2)＿完了</t>
+    <rPh sb="18" eb="20">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームのバグ探し＿完了</t>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・車の配置＿完了
+・プレゼンテーション作成＿途中</t>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>トチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・BGMの実装
+・fainal tester</t>
+    <rPh sb="5" eb="7">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・手に入れた能力の視覚化
+・ポーズ画面の効果音の実装
+・車に轢かれた時の判定実装
+・ゲームオーバーしたときにゲームクリアすると何かが起きる(バグ)</t>
+    <rPh sb="1" eb="2">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>シカクカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>ハンテイジッソウ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・余分なデータの削除
+・自販機のポーズ中に実行できるバグ修正
+・NPCの音設定</t>
+    <rPh sb="1" eb="3">
+      <t>ヨブン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームCLEAR時の効果音の実装
+・能力を手に入れた時に出る残りの時間表示</t>
+    <rPh sb="9" eb="10">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="34" eb="38">
+      <t>ジカンヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2799,7 +2958,7 @@
         <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>6</v>
@@ -2808,7 +2967,7 @@
     <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.4">
       <c r="A39" s="9"/>
       <c r="B39" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>90</v>
@@ -2834,10 +2993,10 @@
         <v>86</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -2846,10 +3005,10 @@
     <row r="42" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>6</v>
@@ -2861,7 +3020,7 @@
         <v>91</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>7</v>
@@ -2870,37 +3029,67 @@
     <row r="44" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A45" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="56.25" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="37.5" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
+      <c r="B48" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A4:A7"/>
@@ -2908,6 +3097,12 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
